--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>136692311</v>
       </c>
       <c r="B5" t="n">
-        <v>93402</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136692320</v>
       </c>
       <c r="B6" t="n">
-        <v>93437</v>
+        <v>93438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136692306</v>
       </c>
       <c r="B14" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136692329</v>
       </c>
       <c r="B15" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136692310</v>
       </c>
       <c r="B17" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136692323</v>
       </c>
       <c r="B21" t="n">
-        <v>93075</v>
+        <v>93076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>136692324</v>
       </c>
       <c r="B22" t="n">
-        <v>93092</v>
+        <v>93093</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>136692331</v>
       </c>
       <c r="B54" t="n">
-        <v>93417</v>
+        <v>93418</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>136692333</v>
       </c>
       <c r="B70" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>136692328</v>
       </c>
       <c r="B72" t="n">
-        <v>93075</v>
+        <v>93076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>136692312</v>
       </c>
       <c r="B105" t="n">
-        <v>93426</v>
+        <v>93427</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ105"/>
+  <dimension ref="A1:AZ107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,7 +993,7 @@
         <v>136692311</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93408</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136692320</v>
       </c>
       <c r="B6" t="n">
-        <v>93438</v>
+        <v>93443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>136692317</v>
       </c>
       <c r="B7" t="n">
-        <v>87496</v>
+        <v>87498</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136692304</v>
       </c>
       <c r="B9" t="n">
-        <v>87586</v>
+        <v>87588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136692307</v>
       </c>
       <c r="B10" t="n">
-        <v>87549</v>
+        <v>87551</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136692334</v>
       </c>
       <c r="B11" t="n">
-        <v>87549</v>
+        <v>87551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136692336</v>
       </c>
       <c r="B12" t="n">
-        <v>87549</v>
+        <v>87551</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136692308</v>
       </c>
       <c r="B13" t="n">
-        <v>91511</v>
+        <v>91513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136692306</v>
       </c>
       <c r="B14" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136692329</v>
       </c>
       <c r="B15" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136692310</v>
       </c>
       <c r="B17" t="n">
-        <v>93400</v>
+        <v>93405</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>136692335</v>
       </c>
       <c r="B19" t="n">
-        <v>89321</v>
+        <v>89323</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136692323</v>
       </c>
       <c r="B21" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>136692324</v>
       </c>
       <c r="B22" t="n">
-        <v>93093</v>
+        <v>93098</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>136692322</v>
       </c>
       <c r="B23" t="n">
-        <v>91616</v>
+        <v>91618</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3211,32 +3211,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>97079058</v>
+        <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>79327</v>
+        <v>93445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3245,17 +3245,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Västra Kalleberget, S om Gärde, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439984</v>
+        <v>440108</v>
       </c>
       <c r="R26" t="n">
-        <v>7048506</v>
+        <v>7048217</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3279,12 +3279,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3297,52 +3297,57 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Gammal blåbärsgranskog i sluttande terräng</t>
+        </is>
+      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97079058</t>
+          <t>https://artportalen.se/Sighting/136692314</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>97079535</v>
+        <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>79327</v>
+        <v>93445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3351,17 +3356,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Västra Kalleberget, S om Gärde, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440008</v>
+        <v>439989</v>
       </c>
       <c r="R27" t="n">
-        <v>7048146</v>
+        <v>7047963</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3385,12 +3390,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3403,65 +3408,73 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97079535</t>
+          <t>https://artportalen.se/Sighting/136692319</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>90799374</v>
+        <v>97079058</v>
       </c>
       <c r="B28" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440120</v>
+        <v>439984</v>
       </c>
       <c r="R28" t="n">
-        <v>7048375</v>
+        <v>7048506</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3488,17 +3501,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3507,18 +3515,9 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3528,64 +3527,63 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90799374</t>
+          <t>https://artportalen.se/Sighting/97079058</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128236793</v>
+        <v>97079535</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439901</v>
+        <v>440008</v>
       </c>
       <c r="R29" t="n">
-        <v>7047874</v>
+        <v>7048146</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3609,17 +3607,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3628,30 +3621,31 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236793</t>
+          <t>https://artportalen.se/Sighting/97079535</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128236794</v>
+        <v>90799374</v>
       </c>
       <c r="B30" t="n">
         <v>57953</v>
@@ -3682,17 +3676,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439899</v>
+        <v>440120</v>
       </c>
       <c r="R30" t="n">
-        <v>7047901</v>
+        <v>7048375</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3716,17 +3710,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3737,28 +3731,42 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236794</t>
+          <t>https://artportalen.se/Sighting/90799374</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128236795</v>
+        <v>128236793</v>
       </c>
       <c r="B31" t="n">
         <v>57953</v>
@@ -3793,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439915</v>
+        <v>439901</v>
       </c>
       <c r="R31" t="n">
-        <v>7047878</v>
+        <v>7047874</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3833,7 +3841,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3859,13 +3867,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236795</t>
+          <t>https://artportalen.se/Sighting/128236793</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128236796</v>
+        <v>128236794</v>
       </c>
       <c r="B32" t="n">
         <v>57953</v>
@@ -3900,10 +3908,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439918</v>
+        <v>439899</v>
       </c>
       <c r="R32" t="n">
-        <v>7047885</v>
+        <v>7047901</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,7 +3948,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3966,13 +3974,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236796</t>
+          <t>https://artportalen.se/Sighting/128236794</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128236797</v>
+        <v>128236795</v>
       </c>
       <c r="B33" t="n">
         <v>57953</v>
@@ -4007,10 +4015,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439930</v>
+        <v>439915</v>
       </c>
       <c r="R33" t="n">
-        <v>7047883</v>
+        <v>7047878</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,7 +4055,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4073,13 +4081,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236797</t>
+          <t>https://artportalen.se/Sighting/128236795</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128236798</v>
+        <v>128236796</v>
       </c>
       <c r="B34" t="n">
         <v>57953</v>
@@ -4114,10 +4122,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440008</v>
+        <v>439918</v>
       </c>
       <c r="R34" t="n">
-        <v>7048019</v>
+        <v>7047885</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4180,13 +4188,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236798</t>
+          <t>https://artportalen.se/Sighting/128236796</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128236799</v>
+        <v>128236797</v>
       </c>
       <c r="B35" t="n">
         <v>57953</v>
@@ -4221,10 +4229,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440022</v>
+        <v>439930</v>
       </c>
       <c r="R35" t="n">
-        <v>7048062</v>
+        <v>7047883</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4261,7 +4269,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4287,13 +4295,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236799</t>
+          <t>https://artportalen.se/Sighting/128236797</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128236800</v>
+        <v>128236798</v>
       </c>
       <c r="B36" t="n">
         <v>57953</v>
@@ -4328,10 +4336,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440015</v>
+        <v>440008</v>
       </c>
       <c r="R36" t="n">
-        <v>7048070</v>
+        <v>7048019</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4394,54 +4402,54 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236800</t>
+          <t>https://artportalen.se/Sighting/128236798</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>91131267</v>
+        <v>128236799</v>
       </c>
       <c r="B37" t="n">
-        <v>99017</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219795</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440002</v>
+        <v>440022</v>
       </c>
       <c r="R37" t="n">
-        <v>7048282</v>
+        <v>7048062</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4465,12 +4473,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,69 +4498,65 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131267</t>
+          <t>https://artportalen.se/Sighting/128236799</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>91131372</v>
+        <v>128236800</v>
       </c>
       <c r="B38" t="n">
-        <v>99017</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219795</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gärdesån-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440013</v>
+        <v>440015</v>
       </c>
       <c r="R38" t="n">
-        <v>7047915</v>
+        <v>7048070</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4571,12 +4580,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4587,40 +4601,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Möjlig kalktallskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131372</t>
+          <t>https://artportalen.se/Sighting/128236800</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>91131313</v>
+        <v>91131267</v>
       </c>
       <c r="B39" t="n">
-        <v>99142</v>
+        <v>99017</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4628,21 +4633,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219847</v>
+        <v>219795</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4652,10 +4657,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440087</v>
+        <v>440002</v>
       </c>
       <c r="R39" t="n">
-        <v>7048509</v>
+        <v>7048282</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4699,16 +4704,6 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
@@ -4727,16 +4722,16 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131313</t>
+          <t>https://artportalen.se/Sighting/91131267</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>91131365</v>
+        <v>91131372</v>
       </c>
       <c r="B40" t="n">
-        <v>99142</v>
+        <v>99017</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,21 +4739,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219847</v>
+        <v>219795</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4768,10 +4763,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440034</v>
+        <v>440013</v>
       </c>
       <c r="R40" t="n">
-        <v>7047876</v>
+        <v>7047915</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4838,16 +4833,16 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131365</t>
+          <t>https://artportalen.se/Sighting/91131372</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>91131308</v>
+        <v>91131313</v>
       </c>
       <c r="B41" t="n">
-        <v>99456</v>
+        <v>99142</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,21 +4850,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219880</v>
+        <v>219847</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4879,10 +4874,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440102</v>
+        <v>440087</v>
       </c>
       <c r="R41" t="n">
-        <v>7048359</v>
+        <v>7048509</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4954,16 +4949,16 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131308</t>
+          <t>https://artportalen.se/Sighting/91131313</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>91131314</v>
+        <v>91131365</v>
       </c>
       <c r="B42" t="n">
-        <v>99456</v>
+        <v>99142</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4971,34 +4966,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219880</v>
+        <v>219847</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440087</v>
+        <v>440034</v>
       </c>
       <c r="R42" t="n">
-        <v>7048509</v>
+        <v>7047876</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5025,12 +5020,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5044,12 +5039,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
+          <t>Möjlig kalktallskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5070,13 +5060,13 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131314</t>
+          <t>https://artportalen.se/Sighting/91131365</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128236803</v>
+        <v>91131308</v>
       </c>
       <c r="B43" t="n">
         <v>99456</v>
@@ -5107,17 +5097,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440092</v>
+        <v>440102</v>
       </c>
       <c r="R43" t="n">
-        <v>7048259</v>
+        <v>7048359</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5141,12 +5131,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5157,31 +5147,45 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236803</t>
+          <t>https://artportalen.se/Sighting/91131308</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>91131370</v>
+        <v>91131314</v>
       </c>
       <c r="B44" t="n">
-        <v>104628</v>
+        <v>99456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5189,34 +5193,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222412</v>
+        <v>219880</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gärdesån-Tångeråsen, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440013</v>
+        <v>440087</v>
       </c>
       <c r="R44" t="n">
-        <v>7047915</v>
+        <v>7048509</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5243,12 +5247,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5262,7 +5266,12 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Möjlig kalktallskog</t>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5283,16 +5292,16 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131370</t>
+          <t>https://artportalen.se/Sighting/91131314</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>91131268</v>
+        <v>128236803</v>
       </c>
       <c r="B45" t="n">
-        <v>101326</v>
+        <v>99456</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5300,37 +5309,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440002</v>
+        <v>440092</v>
       </c>
       <c r="R45" t="n">
-        <v>7048282</v>
+        <v>7048259</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5354,12 +5363,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5374,31 +5383,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131268</t>
+          <t>https://artportalen.se/Sighting/128236803</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>91131309</v>
+        <v>91131370</v>
       </c>
       <c r="B46" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5406,34 +5411,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440102</v>
+        <v>440013</v>
       </c>
       <c r="R46" t="n">
-        <v>7048359</v>
+        <v>7047915</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5460,12 +5465,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5479,12 +5484,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
+          <t>Möjlig kalktallskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5505,13 +5505,13 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131309</t>
+          <t>https://artportalen.se/Sighting/91131370</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>91131311</v>
+        <v>91131268</v>
       </c>
       <c r="B47" t="n">
         <v>101326</v>
@@ -5546,10 +5546,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440076</v>
+        <v>440002</v>
       </c>
       <c r="R47" t="n">
-        <v>7048401</v>
+        <v>7048282</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5593,16 +5593,6 @@
       <c r="AG47" t="b">
         <v>0</v>
       </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
@@ -5621,13 +5611,13 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131311</t>
+          <t>https://artportalen.se/Sighting/91131268</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>91131315</v>
+        <v>91131309</v>
       </c>
       <c r="B48" t="n">
         <v>101326</v>
@@ -5662,10 +5652,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440087</v>
+        <v>440102</v>
       </c>
       <c r="R48" t="n">
-        <v>7048509</v>
+        <v>7048359</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5737,13 +5727,13 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131315</t>
+          <t>https://artportalen.se/Sighting/91131309</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>91131373</v>
+        <v>91131311</v>
       </c>
       <c r="B49" t="n">
         <v>101326</v>
@@ -5774,14 +5764,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gärdesån-Tångeråsen, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440013</v>
+        <v>440076</v>
       </c>
       <c r="R49" t="n">
-        <v>7047915</v>
+        <v>7048401</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5808,12 +5798,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5827,7 +5817,12 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Möjlig kalktallskog</t>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5848,13 +5843,13 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131373</t>
+          <t>https://artportalen.se/Sighting/91131311</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>97079546</v>
+        <v>91131315</v>
       </c>
       <c r="B50" t="n">
         <v>101326</v>
@@ -5883,20 +5878,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440022</v>
+        <v>440087</v>
       </c>
       <c r="R50" t="n">
-        <v>7048186</v>
+        <v>7048509</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5923,12 +5914,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5937,9 +5928,18 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5949,22 +5949,26 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97079546</t>
+          <t>https://artportalen.se/Sighting/91131315</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>90799376</v>
+        <v>91131373</v>
       </c>
       <c r="B51" t="n">
-        <v>99038</v>
+        <v>101326</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,30 +5976,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440087</v>
+        <v>440013</v>
       </c>
       <c r="R51" t="n">
-        <v>7048509</v>
+        <v>7047915</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6022,12 +6030,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6041,12 +6049,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
+          <t>Möjlig kalktallskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6067,54 +6070,58 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90799376</t>
+          <t>https://artportalen.se/Sighting/91131373</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136692305</v>
+        <v>97079546</v>
       </c>
       <c r="B52" t="n">
-        <v>87497</v>
+        <v>101326</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>249228</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västra Kalleberget, S om Gärde, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440121</v>
+        <v>440022</v>
       </c>
       <c r="R52" t="n">
-        <v>7048201</v>
+        <v>7048186</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6138,12 +6145,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6152,76 +6159,68 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Gammal blåbärsgranskog i sluttande terräng</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136692305</t>
+          <t>https://artportalen.se/Sighting/97079546</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136692325</v>
+        <v>90799376</v>
       </c>
       <c r="B53" t="n">
-        <v>87471</v>
+        <v>99038</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6003296</v>
+        <v>223597</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Fr.) Melot</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västra Kalleberget, S om Gärde, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440060</v>
+        <v>440087</v>
       </c>
       <c r="R53" t="n">
-        <v>7048350</v>
+        <v>7048509</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6245,12 +6244,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6264,33 +6263,42 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Bördig, gammal blåbärsgranskog</t>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136692325</t>
+          <t>https://artportalen.se/Sighting/90799376</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136692331</v>
+        <v>136692305</v>
       </c>
       <c r="B54" t="n">
-        <v>93418</v>
+        <v>87499</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6298,19 +6306,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6047725</v>
+        <v>249228</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6318,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>439891</v>
+        <v>440121</v>
       </c>
       <c r="R54" t="n">
-        <v>7048259</v>
+        <v>7048201</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6367,7 +6379,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Gammal, bördig blåbärsgranskog</t>
+          <t>Gammal blåbärsgranskog i sluttande terräng</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6384,51 +6396,51 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136692331</t>
+          <t>https://artportalen.se/Sighting/136692305</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128236805</v>
+        <v>136692325</v>
       </c>
       <c r="B55" t="n">
-        <v>91905</v>
+        <v>87473</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>6003296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Västra Kalleberget, S om Gärde, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440069</v>
+        <v>440060</v>
       </c>
       <c r="R55" t="n">
-        <v>7047632</v>
+        <v>7048350</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6455,12 +6467,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6471,31 +6483,36 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Bördig, gammal blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236805</t>
+          <t>https://artportalen.se/Sighting/136692325</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128236806</v>
+        <v>136692331</v>
       </c>
       <c r="B56" t="n">
-        <v>91905</v>
+        <v>93423</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,34 +6520,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>6047725</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Västra Kalleberget, S om Gärde, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440074</v>
+        <v>439891</v>
       </c>
       <c r="R56" t="n">
-        <v>7047804</v>
+        <v>7048259</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6557,12 +6570,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6573,28 +6586,33 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Gammal, bördig blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236806</t>
+          <t>https://artportalen.se/Sighting/136692331</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128236808</v>
+        <v>128236805</v>
       </c>
       <c r="B57" t="n">
         <v>91905</v>
@@ -6629,10 +6647,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440068</v>
+        <v>440069</v>
       </c>
       <c r="R57" t="n">
-        <v>7047806</v>
+        <v>7047632</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6690,13 +6708,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236808</t>
+          <t>https://artportalen.se/Sighting/128236805</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128236810</v>
+        <v>128236806</v>
       </c>
       <c r="B58" t="n">
         <v>91905</v>
@@ -6731,10 +6749,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439966</v>
+        <v>440074</v>
       </c>
       <c r="R58" t="n">
-        <v>7047817</v>
+        <v>7047804</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6792,57 +6810,54 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236810</t>
+          <t>https://artportalen.se/Sighting/128236806</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>97079510</v>
+        <v>128236808</v>
       </c>
       <c r="B59" t="n">
-        <v>79327</v>
+        <v>91905</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440090</v>
+        <v>440068</v>
       </c>
       <c r="R59" t="n">
-        <v>7047637</v>
+        <v>7047806</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6866,12 +6881,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6880,75 +6895,71 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97079510</t>
+          <t>https://artportalen.se/Sighting/128236808</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>97079525</v>
+        <v>128236810</v>
       </c>
       <c r="B60" t="n">
-        <v>79327</v>
+        <v>91905</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>439925</v>
+        <v>439966</v>
       </c>
       <c r="R60" t="n">
-        <v>7047803</v>
+        <v>7047817</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6972,12 +6983,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6986,72 +6997,74 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97079525</t>
+          <t>https://artportalen.se/Sighting/128236810</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128236783</v>
+        <v>97079510</v>
       </c>
       <c r="B61" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440150</v>
+        <v>440090</v>
       </c>
       <c r="R61" t="n">
-        <v>7047992</v>
+        <v>7047637</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7075,17 +7088,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7094,71 +7102,75 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236783</t>
+          <t>https://artportalen.se/Sighting/97079510</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128236790</v>
+        <v>97079525</v>
       </c>
       <c r="B62" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>439938</v>
+        <v>439925</v>
       </c>
       <c r="R62" t="n">
-        <v>7047820</v>
+        <v>7047803</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7182,17 +7194,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7201,30 +7208,31 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236790</t>
+          <t>https://artportalen.se/Sighting/97079525</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128236791</v>
+        <v>128236783</v>
       </c>
       <c r="B63" t="n">
         <v>57953</v>
@@ -7259,10 +7267,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>439922</v>
+        <v>440150</v>
       </c>
       <c r="R63" t="n">
-        <v>7047845</v>
+        <v>7047992</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7325,13 +7333,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236791</t>
+          <t>https://artportalen.se/Sighting/128236783</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128236792</v>
+        <v>128236790</v>
       </c>
       <c r="B64" t="n">
         <v>57953</v>
@@ -7366,10 +7374,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>439926</v>
+        <v>439938</v>
       </c>
       <c r="R64" t="n">
-        <v>7047844</v>
+        <v>7047820</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7432,54 +7440,54 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236792</t>
+          <t>https://artportalen.se/Sighting/128236790</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>91131356</v>
+        <v>128236791</v>
       </c>
       <c r="B65" t="n">
-        <v>101326</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gärdesån_Ö3-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440072</v>
+        <v>439922</v>
       </c>
       <c r="R65" t="n">
-        <v>7047691</v>
+        <v>7047845</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7503,12 +7511,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7519,40 +7532,31 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>Möjlig kalktallskog</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131356</t>
+          <t>https://artportalen.se/Sighting/128236791</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>90799475</v>
+        <v>128236792</v>
       </c>
       <c r="B66" t="n">
-        <v>80433</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7560,37 +7564,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440583</v>
+        <v>439926</v>
       </c>
       <c r="R66" t="n">
-        <v>7047416</v>
+        <v>7047844</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7614,12 +7618,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7630,50 +7639,31 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Äldre sälg</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90799475</t>
+          <t>https://artportalen.se/Sighting/128236792</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128236781</v>
+        <v>91131356</v>
       </c>
       <c r="B67" t="n">
-        <v>92632</v>
+        <v>101326</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7681,37 +7671,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3298</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärdesån_Ö3-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440483</v>
+        <v>440072</v>
       </c>
       <c r="R67" t="n">
-        <v>7047353</v>
+        <v>7047691</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7735,12 +7725,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7751,65 +7741,78 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Möjlig kalktallskog</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236781</t>
+          <t>https://artportalen.se/Sighting/91131356</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136692313</v>
+        <v>90799475</v>
       </c>
       <c r="B68" t="n">
-        <v>87586</v>
+        <v>80433</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3624</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Västra Kalleberget, S om Gärde, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440366</v>
+        <v>440583</v>
       </c>
       <c r="R68" t="n">
-        <v>7047394</v>
+        <v>7047416</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7833,12 +7836,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7852,33 +7855,47 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Örtrik, fuktig grannaturskog</t>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Äldre sälg</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136692313</t>
+          <t>https://artportalen.se/Sighting/90799475</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136692316</v>
+        <v>128236781</v>
       </c>
       <c r="B69" t="n">
-        <v>87586</v>
+        <v>92632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7886,30 +7903,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3624</v>
+        <v>3298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Västra Kalleberget, S om Gärde, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440224</v>
+        <v>440483</v>
       </c>
       <c r="R69" t="n">
-        <v>7048082</v>
+        <v>7047353</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7936,12 +7957,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7952,60 +7973,51 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Bördig, gammal blåbärsgranskog</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136692316</t>
+          <t>https://artportalen.se/Sighting/128236781</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136692333</v>
+        <v>136692313</v>
       </c>
       <c r="B70" t="n">
-        <v>93416</v>
+        <v>87588</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4366</v>
+        <v>3624</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Banker</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8013,10 +8025,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440397</v>
+        <v>440366</v>
       </c>
       <c r="R70" t="n">
-        <v>7047397</v>
+        <v>7047394</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8062,7 +8074,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Bördig, gammal blåbärsgranskog</t>
+          <t>Örtrik, fuktig grannaturskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8079,40 +8091,36 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136692333</t>
+          <t>https://artportalen.se/Sighting/136692313</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136692332</v>
+        <v>136692316</v>
       </c>
       <c r="B71" t="n">
-        <v>89316</v>
+        <v>87588</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4404</v>
+        <v>3624</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sotvaxskivling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hygrophorus camarophyllus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8120,10 +8128,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440310</v>
+        <v>440224</v>
       </c>
       <c r="R71" t="n">
-        <v>7047411</v>
+        <v>7048082</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8169,7 +8177,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Sluten, gammal blåbärsgranskog</t>
+          <t>Bördig, gammal blåbärsgranskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8186,38 +8194,38 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136692332</t>
+          <t>https://artportalen.se/Sighting/136692316</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136692328</v>
+        <v>136692333</v>
       </c>
       <c r="B72" t="n">
-        <v>93076</v>
+        <v>93421</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8227,10 +8235,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440281</v>
+        <v>440397</v>
       </c>
       <c r="R72" t="n">
-        <v>7047254</v>
+        <v>7047397</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8276,7 +8284,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Tät, örtrik grannaturskog</t>
+          <t>Bördig, gammal blåbärsgranskog</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8293,16 +8301,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136692328</t>
+          <t>https://artportalen.se/Sighting/136692333</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>97079043</v>
+        <v>136692332</v>
       </c>
       <c r="B73" t="n">
-        <v>93233</v>
+        <v>89318</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8310,40 +8318,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5964</v>
+        <v>4404</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Västra Kalleberget, S om Gärde, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440025</v>
+        <v>440310</v>
       </c>
       <c r="R73" t="n">
-        <v>7048663</v>
+        <v>7047411</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8367,12 +8372,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8381,75 +8386,76 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Sluten, gammal blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97079043</t>
+          <t>https://artportalen.se/Sighting/136692332</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>97079052</v>
+        <v>136692328</v>
       </c>
       <c r="B74" t="n">
-        <v>79327</v>
+        <v>93081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Västra Kalleberget, S om Gärde, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>439994</v>
+        <v>440281</v>
       </c>
       <c r="R74" t="n">
-        <v>7048628</v>
+        <v>7047254</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8473,12 +8479,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8487,56 +8493,60 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Tät, örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97079052</t>
+          <t>https://artportalen.se/Sighting/136692328</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>97079295</v>
+        <v>97079043</v>
       </c>
       <c r="B75" t="n">
-        <v>79327</v>
+        <v>93233</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8549,10 +8559,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440341</v>
+        <v>440025</v>
       </c>
       <c r="R75" t="n">
-        <v>7047930</v>
+        <v>7048663</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8587,11 +8597,6 @@
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8616,13 +8621,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97079295</t>
+          <t>https://artportalen.se/Sighting/97079043</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128236817</v>
+        <v>97079052</v>
       </c>
       <c r="B76" t="n">
         <v>79327</v>
@@ -8651,19 +8656,22 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440606</v>
+        <v>439994</v>
       </c>
       <c r="R76" t="n">
-        <v>7047293</v>
+        <v>7048628</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8687,17 +8695,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8706,68 +8709,72 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236817</t>
+          <t>https://artportalen.se/Sighting/97079052</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>90799389</v>
+        <v>97079295</v>
       </c>
       <c r="B77" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440153</v>
+        <v>440341</v>
       </c>
       <c r="R77" t="n">
-        <v>7048204</v>
+        <v>7047930</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8794,12 +8801,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8808,18 +8820,9 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Sälgar (flera)</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8829,64 +8832,60 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90799389</t>
+          <t>https://artportalen.se/Sighting/97079295</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>90799458</v>
+        <v>128236817</v>
       </c>
       <c r="B78" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440422</v>
+        <v>440606</v>
       </c>
       <c r="R78" t="n">
-        <v>7047763</v>
+        <v>7047293</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8910,17 +8909,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8931,47 +8930,28 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Äldre sälg</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90799458</t>
+          <t>https://artportalen.se/Sighting/128236817</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>90799473</v>
+        <v>90799389</v>
       </c>
       <c r="B79" t="n">
         <v>80432</v>
@@ -9006,10 +8986,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440583</v>
+        <v>440153</v>
       </c>
       <c r="R79" t="n">
-        <v>7047416</v>
+        <v>7048204</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9060,12 +9040,7 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Äldre sälg</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
+          <t>Sälgar (flera)</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9086,13 +9061,13 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90799473</t>
+          <t>https://artportalen.se/Sighting/90799389</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>97079293</v>
+        <v>90799458</v>
       </c>
       <c r="B80" t="n">
         <v>80432</v>
@@ -9121,19 +9096,16 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440341</v>
+        <v>440422</v>
       </c>
       <c r="R80" t="n">
-        <v>7047930</v>
+        <v>7047763</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9160,12 +9132,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9174,9 +9151,23 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Äldre sälg</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9186,44 +9177,48 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97079293</t>
+          <t>https://artportalen.se/Sighting/90799458</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>90799390</v>
+        <v>90799473</v>
       </c>
       <c r="B81" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9233,10 +9228,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440153</v>
+        <v>440583</v>
       </c>
       <c r="R81" t="n">
-        <v>7048204</v>
+        <v>7047416</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9287,7 +9282,12 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Sälgar (flera)</t>
+          <t>Äldre sälg</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9308,51 +9308,54 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90799390</t>
+          <t>https://artportalen.se/Sighting/90799473</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>90799470</v>
+        <v>97079293</v>
       </c>
       <c r="B82" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440583</v>
+        <v>440341</v>
       </c>
       <c r="R82" t="n">
-        <v>7047416</v>
+        <v>7047930</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9379,12 +9382,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9393,23 +9396,9 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Äldre sälg</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9419,26 +9408,22 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90799470</t>
+          <t>https://artportalen.se/Sighting/97079293</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>90799394</v>
+        <v>90799390</v>
       </c>
       <c r="B83" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9446,21 +9431,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9545,16 +9530,16 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90799394</t>
+          <t>https://artportalen.se/Sighting/90799390</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>90799392</v>
+        <v>90799470</v>
       </c>
       <c r="B84" t="n">
-        <v>80468</v>
+        <v>80461</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9562,21 +9547,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9586,10 +9571,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440153</v>
+        <v>440583</v>
       </c>
       <c r="R84" t="n">
-        <v>7048204</v>
+        <v>7047416</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9640,7 +9625,12 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Sälgar (flera)</t>
+          <t>Äldre sälg</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9661,55 +9651,51 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90799392</t>
+          <t>https://artportalen.se/Sighting/90799470</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>97079272</v>
+        <v>90799394</v>
       </c>
       <c r="B85" t="n">
-        <v>57953</v>
+        <v>80467</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440215</v>
+        <v>440153</v>
       </c>
       <c r="R85" t="n">
-        <v>7048160</v>
+        <v>7048204</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9736,17 +9722,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9757,6 +9738,16 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Sälgar (flera)</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -9766,60 +9757,64 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97079272</t>
+          <t>https://artportalen.se/Sighting/90799394</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128236782</v>
+        <v>90799392</v>
       </c>
       <c r="B86" t="n">
-        <v>57953</v>
+        <v>80468</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440231</v>
+        <v>440153</v>
       </c>
       <c r="R86" t="n">
-        <v>7048069</v>
+        <v>7048204</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9843,17 +9838,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9864,28 +9854,42 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Sälgar (flera)</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236782</t>
+          <t>https://artportalen.se/Sighting/90799392</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128236784</v>
+        <v>97079272</v>
       </c>
       <c r="B87" t="n">
         <v>57953</v>
@@ -9914,19 +9918,23 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440471</v>
+        <v>440215</v>
       </c>
       <c r="R87" t="n">
-        <v>7047318</v>
+        <v>7048160</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9950,17 +9958,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9975,24 +9983,24 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236784</t>
+          <t>https://artportalen.se/Sighting/97079272</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128236785</v>
+        <v>128236782</v>
       </c>
       <c r="B88" t="n">
         <v>57953</v>
@@ -10027,10 +10035,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440476</v>
+        <v>440231</v>
       </c>
       <c r="R88" t="n">
-        <v>7047442</v>
+        <v>7048069</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10093,13 +10101,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236785</t>
+          <t>https://artportalen.se/Sighting/128236782</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128236786</v>
+        <v>128236784</v>
       </c>
       <c r="B89" t="n">
         <v>57953</v>
@@ -10134,10 +10142,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440548</v>
+        <v>440471</v>
       </c>
       <c r="R89" t="n">
-        <v>7047339</v>
+        <v>7047318</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10200,13 +10208,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236786</t>
+          <t>https://artportalen.se/Sighting/128236784</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128236788</v>
+        <v>128236785</v>
       </c>
       <c r="B90" t="n">
         <v>57953</v>
@@ -10241,10 +10249,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440530</v>
+        <v>440476</v>
       </c>
       <c r="R90" t="n">
-        <v>7047514</v>
+        <v>7047442</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10307,13 +10315,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236788</t>
+          <t>https://artportalen.se/Sighting/128236785</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128236789</v>
+        <v>128236786</v>
       </c>
       <c r="B91" t="n">
         <v>57953</v>
@@ -10348,10 +10356,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>440467</v>
+        <v>440548</v>
       </c>
       <c r="R91" t="n">
-        <v>7047649</v>
+        <v>7047339</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10414,54 +10422,54 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128236789</t>
+          <t>https://artportalen.se/Sighting/128236786</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>90799380</v>
+        <v>128236788</v>
       </c>
       <c r="B92" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440159</v>
+        <v>440530</v>
       </c>
       <c r="R92" t="n">
-        <v>7048144</v>
+        <v>7047514</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10485,17 +10493,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Synobs av tjäder</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10506,78 +10514,69 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90799380</t>
+          <t>https://artportalen.se/Sighting/128236788</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>91131389</v>
+        <v>128236789</v>
       </c>
       <c r="B93" t="n">
-        <v>99017</v>
+        <v>57953</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219795</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440284</v>
+        <v>440467</v>
       </c>
       <c r="R93" t="n">
-        <v>7047388</v>
+        <v>7047649</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10601,12 +10600,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10617,45 +10621,31 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131389</t>
+          <t>https://artportalen.se/Sighting/128236789</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>91131398</v>
+        <v>90799380</v>
       </c>
       <c r="B94" t="n">
-        <v>99456</v>
+        <v>57141</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10663,21 +10653,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219880</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10687,10 +10677,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440465</v>
+        <v>440159</v>
       </c>
       <c r="R94" t="n">
-        <v>7047361</v>
+        <v>7048144</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10725,6 +10715,11 @@
           <t>2019-07-16</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Synobs av tjäder</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10737,11 +10732,6 @@
       <c r="AI94" t="inlineStr">
         <is>
           <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10762,16 +10752,16 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131398</t>
+          <t>https://artportalen.se/Sighting/90799380</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>91131407</v>
+        <v>91131389</v>
       </c>
       <c r="B95" t="n">
-        <v>99456</v>
+        <v>99017</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10779,21 +10769,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219880</v>
+        <v>219795</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10803,10 +10793,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440565</v>
+        <v>440284</v>
       </c>
       <c r="R95" t="n">
-        <v>7047324</v>
+        <v>7047388</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10878,16 +10868,16 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131407</t>
+          <t>https://artportalen.se/Sighting/91131389</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>91131405</v>
+        <v>91131398</v>
       </c>
       <c r="B96" t="n">
-        <v>98030</v>
+        <v>99456</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10895,21 +10885,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221063</v>
+        <v>219880</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10919,10 +10909,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440565</v>
+        <v>440465</v>
       </c>
       <c r="R96" t="n">
-        <v>7047324</v>
+        <v>7047361</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10994,16 +10984,16 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131405</t>
+          <t>https://artportalen.se/Sighting/91131398</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>91131382</v>
+        <v>91131407</v>
       </c>
       <c r="B97" t="n">
-        <v>104628</v>
+        <v>99456</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11011,21 +11001,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222412</v>
+        <v>219880</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11035,10 +11025,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440284</v>
+        <v>440565</v>
       </c>
       <c r="R97" t="n">
-        <v>7047388</v>
+        <v>7047324</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11110,16 +11100,16 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131382</t>
+          <t>https://artportalen.se/Sighting/91131407</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>91131396</v>
+        <v>91131405</v>
       </c>
       <c r="B98" t="n">
-        <v>104628</v>
+        <v>98030</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11127,21 +11117,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222412</v>
+        <v>221063</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11151,10 +11141,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440465</v>
+        <v>440565</v>
       </c>
       <c r="R98" t="n">
-        <v>7047361</v>
+        <v>7047324</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11226,16 +11216,16 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131396</t>
+          <t>https://artportalen.se/Sighting/91131405</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>90799381</v>
+        <v>91131382</v>
       </c>
       <c r="B99" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11243,21 +11233,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11267,10 +11257,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440159</v>
+        <v>440284</v>
       </c>
       <c r="R99" t="n">
-        <v>7048144</v>
+        <v>7047388</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11305,11 +11295,6 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Synobs av tjäder</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -11322,6 +11307,11 @@
       <c r="AI99" t="inlineStr">
         <is>
           <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11342,16 +11332,16 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90799381</t>
+          <t>https://artportalen.se/Sighting/91131382</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>90799468</v>
+        <v>91131396</v>
       </c>
       <c r="B100" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11359,21 +11349,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11383,10 +11373,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440636</v>
+        <v>440465</v>
       </c>
       <c r="R100" t="n">
-        <v>7047294</v>
+        <v>7047361</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11458,13 +11448,13 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90799468</t>
+          <t>https://artportalen.se/Sighting/91131396</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>91131390</v>
+        <v>90799381</v>
       </c>
       <c r="B101" t="n">
         <v>101326</v>
@@ -11499,10 +11489,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440284</v>
+        <v>440159</v>
       </c>
       <c r="R101" t="n">
-        <v>7047388</v>
+        <v>7048144</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11537,6 +11527,11 @@
           <t>2019-07-16</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Synobs av tjäder</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11549,11 +11544,6 @@
       <c r="AI101" t="inlineStr">
         <is>
           <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11574,13 +11564,13 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131390</t>
+          <t>https://artportalen.se/Sighting/90799381</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>91131401</v>
+        <v>90799468</v>
       </c>
       <c r="B102" t="n">
         <v>101326</v>
@@ -11615,10 +11605,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440465</v>
+        <v>440636</v>
       </c>
       <c r="R102" t="n">
-        <v>7047361</v>
+        <v>7047294</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11690,13 +11680,13 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131401</t>
+          <t>https://artportalen.se/Sighting/90799468</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>91131408</v>
+        <v>91131390</v>
       </c>
       <c r="B103" t="n">
         <v>101326</v>
@@ -11731,10 +11721,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440565</v>
+        <v>440284</v>
       </c>
       <c r="R103" t="n">
-        <v>7047324</v>
+        <v>7047388</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11806,16 +11796,16 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91131408</t>
+          <t>https://artportalen.se/Sighting/91131390</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>90799460</v>
+        <v>91131401</v>
       </c>
       <c r="B104" t="n">
-        <v>80392</v>
+        <v>101326</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11823,21 +11813,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11847,10 +11837,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440422</v>
+        <v>440465</v>
       </c>
       <c r="R104" t="n">
-        <v>7047763</v>
+        <v>7047361</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11885,11 +11875,6 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -11902,11 +11887,6 @@
       <c r="AI104" t="inlineStr">
         <is>
           <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Äldre sälg</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
@@ -11932,57 +11912,54 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90799460</t>
+          <t>https://artportalen.se/Sighting/91131401</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>136692312</v>
+        <v>91131408</v>
       </c>
       <c r="B105" t="n">
-        <v>93427</v>
+        <v>101326</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6331649</v>
+        <v>222498</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Huldretaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellodon dititomentosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Svantesson</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Västra Kalleberget, S om Gärde, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440412</v>
+        <v>440565</v>
       </c>
       <c r="R105" t="n">
-        <v>7047391</v>
+        <v>7047324</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12006,17 +11983,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Halvgissning. I ren granskog och fruktkropparna är inte gyttrade. Kollekt finns.</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12025,28 +11997,278 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Bördig, gammal blåbärsgranskog</t>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131408</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>90799460</v>
+      </c>
+      <c r="B106" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>440422</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7047763</v>
+      </c>
+      <c r="S106" t="n">
+        <v>25</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Äldre sälg</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799460</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>136692312</v>
+      </c>
+      <c r="B107" t="n">
+        <v>93432</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6331649</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Huldretaggsvamp</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Phellodon dititomentosus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Svantesson</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Västra Kalleberget, S om Gärde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>440412</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7047391</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Halvgissning. I ren granskog och fruktkropparna är inte gyttrade. Kollekt finns.</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Bördig, gammal blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
+      <c r="AX107" t="inlineStr">
         <is>
           <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
-      <c r="AY105" t="inlineStr"/>
-      <c r="AZ105" t="inlineStr">
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136692312</t>
         </is>
@@ -12158,6 +12380,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>136692311</v>
       </c>
       <c r="B5" t="n">
-        <v>93408</v>
+        <v>93410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136692320</v>
       </c>
       <c r="B6" t="n">
-        <v>93443</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>136692317</v>
       </c>
       <c r="B7" t="n">
-        <v>87498</v>
+        <v>87500</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136692304</v>
       </c>
       <c r="B9" t="n">
-        <v>87588</v>
+        <v>87590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136692307</v>
       </c>
       <c r="B10" t="n">
-        <v>87551</v>
+        <v>87553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136692334</v>
       </c>
       <c r="B11" t="n">
-        <v>87551</v>
+        <v>87553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136692336</v>
       </c>
       <c r="B12" t="n">
-        <v>87551</v>
+        <v>87553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136692308</v>
       </c>
       <c r="B13" t="n">
-        <v>91513</v>
+        <v>91515</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136692306</v>
       </c>
       <c r="B14" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136692329</v>
       </c>
       <c r="B15" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136692310</v>
       </c>
       <c r="B17" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>136692335</v>
       </c>
       <c r="B19" t="n">
-        <v>89323</v>
+        <v>89325</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136692323</v>
       </c>
       <c r="B21" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>136692324</v>
       </c>
       <c r="B22" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>136692322</v>
       </c>
       <c r="B23" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>136692305</v>
       </c>
       <c r="B54" t="n">
-        <v>87499</v>
+        <v>87501</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>136692325</v>
       </c>
       <c r="B55" t="n">
-        <v>87473</v>
+        <v>87475</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136692331</v>
       </c>
       <c r="B56" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>136692313</v>
       </c>
       <c r="B70" t="n">
-        <v>87588</v>
+        <v>87590</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136692316</v>
       </c>
       <c r="B71" t="n">
-        <v>87588</v>
+        <v>87590</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>136692333</v>
       </c>
       <c r="B72" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>136692332</v>
       </c>
       <c r="B73" t="n">
-        <v>89318</v>
+        <v>89320</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>136692328</v>
       </c>
       <c r="B74" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>136692312</v>
       </c>
       <c r="B107" t="n">
-        <v>93432</v>
+        <v>93434</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>136692311</v>
       </c>
       <c r="B5" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136692320</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>136692317</v>
       </c>
       <c r="B7" t="n">
-        <v>87500</v>
+        <v>87502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136692304</v>
       </c>
       <c r="B9" t="n">
-        <v>87590</v>
+        <v>87592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136692307</v>
       </c>
       <c r="B10" t="n">
-        <v>87553</v>
+        <v>87555</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136692334</v>
       </c>
       <c r="B11" t="n">
-        <v>87553</v>
+        <v>87555</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136692336</v>
       </c>
       <c r="B12" t="n">
-        <v>87553</v>
+        <v>87555</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136692308</v>
       </c>
       <c r="B13" t="n">
-        <v>91515</v>
+        <v>91517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136692306</v>
       </c>
       <c r="B14" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136692329</v>
       </c>
       <c r="B15" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136692310</v>
       </c>
       <c r="B17" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>136692335</v>
       </c>
       <c r="B19" t="n">
-        <v>89325</v>
+        <v>89327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136692323</v>
       </c>
       <c r="B21" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>136692324</v>
       </c>
       <c r="B22" t="n">
-        <v>93100</v>
+        <v>93102</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>136692322</v>
       </c>
       <c r="B23" t="n">
-        <v>91620</v>
+        <v>91622</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>136692305</v>
       </c>
       <c r="B54" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>136692325</v>
       </c>
       <c r="B55" t="n">
-        <v>87475</v>
+        <v>87477</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136692331</v>
       </c>
       <c r="B56" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>136692313</v>
       </c>
       <c r="B70" t="n">
-        <v>87590</v>
+        <v>87592</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136692316</v>
       </c>
       <c r="B71" t="n">
-        <v>87590</v>
+        <v>87592</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>136692333</v>
       </c>
       <c r="B72" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>136692332</v>
       </c>
       <c r="B73" t="n">
-        <v>89320</v>
+        <v>89322</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>136692328</v>
       </c>
       <c r="B74" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>136692312</v>
       </c>
       <c r="B107" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>136692311</v>
       </c>
       <c r="B5" t="n">
-        <v>93412</v>
+        <v>93414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136692320</v>
       </c>
       <c r="B6" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>136692317</v>
       </c>
       <c r="B7" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136692304</v>
       </c>
       <c r="B9" t="n">
-        <v>87592</v>
+        <v>87594</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136692307</v>
       </c>
       <c r="B10" t="n">
-        <v>87555</v>
+        <v>87557</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136692334</v>
       </c>
       <c r="B11" t="n">
-        <v>87555</v>
+        <v>87557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136692336</v>
       </c>
       <c r="B12" t="n">
-        <v>87555</v>
+        <v>87557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136692308</v>
       </c>
       <c r="B13" t="n">
-        <v>91517</v>
+        <v>91519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136692306</v>
       </c>
       <c r="B14" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136692329</v>
       </c>
       <c r="B15" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136692310</v>
       </c>
       <c r="B17" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>136692335</v>
       </c>
       <c r="B19" t="n">
-        <v>89327</v>
+        <v>89329</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136692323</v>
       </c>
       <c r="B21" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>136692324</v>
       </c>
       <c r="B22" t="n">
-        <v>93102</v>
+        <v>93104</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>136692322</v>
       </c>
       <c r="B23" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>136692305</v>
       </c>
       <c r="B54" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>136692325</v>
       </c>
       <c r="B55" t="n">
-        <v>87477</v>
+        <v>87479</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136692331</v>
       </c>
       <c r="B56" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>136692313</v>
       </c>
       <c r="B70" t="n">
-        <v>87592</v>
+        <v>87594</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136692316</v>
       </c>
       <c r="B71" t="n">
-        <v>87592</v>
+        <v>87594</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>136692333</v>
       </c>
       <c r="B72" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>136692332</v>
       </c>
       <c r="B73" t="n">
-        <v>89322</v>
+        <v>89324</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>136692328</v>
       </c>
       <c r="B74" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>136692312</v>
       </c>
       <c r="B107" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>136692311</v>
       </c>
       <c r="B5" t="n">
-        <v>93414</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136692320</v>
       </c>
       <c r="B6" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>136692317</v>
       </c>
       <c r="B7" t="n">
-        <v>87504</v>
+        <v>87505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136692304</v>
       </c>
       <c r="B9" t="n">
-        <v>87594</v>
+        <v>87595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136692307</v>
       </c>
       <c r="B10" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136692334</v>
       </c>
       <c r="B11" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136692336</v>
       </c>
       <c r="B12" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136692308</v>
       </c>
       <c r="B13" t="n">
-        <v>91519</v>
+        <v>91520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136692306</v>
       </c>
       <c r="B14" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136692329</v>
       </c>
       <c r="B15" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136692310</v>
       </c>
       <c r="B17" t="n">
-        <v>93411</v>
+        <v>93412</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>136692335</v>
       </c>
       <c r="B19" t="n">
-        <v>89329</v>
+        <v>89330</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136692323</v>
       </c>
       <c r="B21" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>136692324</v>
       </c>
       <c r="B22" t="n">
-        <v>93104</v>
+        <v>93105</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>136692322</v>
       </c>
       <c r="B23" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>136692305</v>
       </c>
       <c r="B54" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>136692325</v>
       </c>
       <c r="B55" t="n">
-        <v>87479</v>
+        <v>87480</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136692331</v>
       </c>
       <c r="B56" t="n">
-        <v>93429</v>
+        <v>93430</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>136692313</v>
       </c>
       <c r="B70" t="n">
-        <v>87594</v>
+        <v>87595</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136692316</v>
       </c>
       <c r="B71" t="n">
-        <v>87594</v>
+        <v>87595</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>136692333</v>
       </c>
       <c r="B72" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>136692332</v>
       </c>
       <c r="B73" t="n">
-        <v>89324</v>
+        <v>89325</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>136692328</v>
       </c>
       <c r="B74" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>136692312</v>
       </c>
       <c r="B107" t="n">
-        <v>93438</v>
+        <v>93439</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>136692311</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93421</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136692320</v>
       </c>
       <c r="B6" t="n">
-        <v>93450</v>
+        <v>93456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>136692317</v>
       </c>
       <c r="B7" t="n">
-        <v>87505</v>
+        <v>87511</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136692304</v>
       </c>
       <c r="B9" t="n">
-        <v>87595</v>
+        <v>87601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136692307</v>
       </c>
       <c r="B10" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136692334</v>
       </c>
       <c r="B11" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136692336</v>
       </c>
       <c r="B12" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136692308</v>
       </c>
       <c r="B13" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136692306</v>
       </c>
       <c r="B14" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136692329</v>
       </c>
       <c r="B15" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136692310</v>
       </c>
       <c r="B17" t="n">
-        <v>93412</v>
+        <v>93418</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>136692335</v>
       </c>
       <c r="B19" t="n">
-        <v>89330</v>
+        <v>89336</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136692323</v>
       </c>
       <c r="B21" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>136692324</v>
       </c>
       <c r="B22" t="n">
-        <v>93105</v>
+        <v>93111</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>136692322</v>
       </c>
       <c r="B23" t="n">
-        <v>91625</v>
+        <v>91631</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>136692305</v>
       </c>
       <c r="B54" t="n">
-        <v>87506</v>
+        <v>87512</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>136692325</v>
       </c>
       <c r="B55" t="n">
-        <v>87480</v>
+        <v>87486</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136692331</v>
       </c>
       <c r="B56" t="n">
-        <v>93430</v>
+        <v>93436</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>136692313</v>
       </c>
       <c r="B70" t="n">
-        <v>87595</v>
+        <v>87601</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136692316</v>
       </c>
       <c r="B71" t="n">
-        <v>87595</v>
+        <v>87601</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>136692333</v>
       </c>
       <c r="B72" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>136692332</v>
       </c>
       <c r="B73" t="n">
-        <v>89325</v>
+        <v>89331</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>136692328</v>
       </c>
       <c r="B74" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>136692312</v>
       </c>
       <c r="B107" t="n">
-        <v>93439</v>
+        <v>93445</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>136692311</v>
       </c>
       <c r="B5" t="n">
-        <v>93421</v>
+        <v>93425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136692320</v>
       </c>
       <c r="B6" t="n">
-        <v>93456</v>
+        <v>93460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>136692317</v>
       </c>
       <c r="B7" t="n">
-        <v>87511</v>
+        <v>87515</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136692304</v>
       </c>
       <c r="B9" t="n">
-        <v>87601</v>
+        <v>87605</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136692307</v>
       </c>
       <c r="B10" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136692334</v>
       </c>
       <c r="B11" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136692336</v>
       </c>
       <c r="B12" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136692308</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>91530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136692306</v>
       </c>
       <c r="B14" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136692329</v>
       </c>
       <c r="B15" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136692310</v>
       </c>
       <c r="B17" t="n">
-        <v>93418</v>
+        <v>93422</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>136692335</v>
       </c>
       <c r="B19" t="n">
-        <v>89336</v>
+        <v>89340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136692323</v>
       </c>
       <c r="B21" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>136692324</v>
       </c>
       <c r="B22" t="n">
-        <v>93111</v>
+        <v>93115</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>136692322</v>
       </c>
       <c r="B23" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>136692305</v>
       </c>
       <c r="B54" t="n">
-        <v>87512</v>
+        <v>87516</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>136692325</v>
       </c>
       <c r="B55" t="n">
-        <v>87486</v>
+        <v>87490</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136692331</v>
       </c>
       <c r="B56" t="n">
-        <v>93436</v>
+        <v>93440</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>136692313</v>
       </c>
       <c r="B70" t="n">
-        <v>87601</v>
+        <v>87605</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136692316</v>
       </c>
       <c r="B71" t="n">
-        <v>87601</v>
+        <v>87605</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>136692333</v>
       </c>
       <c r="B72" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>136692332</v>
       </c>
       <c r="B73" t="n">
-        <v>89331</v>
+        <v>89335</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>136692328</v>
       </c>
       <c r="B74" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>136692312</v>
       </c>
       <c r="B107" t="n">
-        <v>93445</v>
+        <v>93449</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>136692311</v>
       </c>
       <c r="B5" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136692320</v>
       </c>
       <c r="B6" t="n">
-        <v>93460</v>
+        <v>93462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>136692317</v>
       </c>
       <c r="B7" t="n">
-        <v>87515</v>
+        <v>87517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136692304</v>
       </c>
       <c r="B9" t="n">
-        <v>87605</v>
+        <v>87607</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136692307</v>
       </c>
       <c r="B10" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136692334</v>
       </c>
       <c r="B11" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136692336</v>
       </c>
       <c r="B12" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136692308</v>
       </c>
       <c r="B13" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136692306</v>
       </c>
       <c r="B14" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136692329</v>
       </c>
       <c r="B15" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136692310</v>
       </c>
       <c r="B17" t="n">
-        <v>93422</v>
+        <v>93424</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>136692335</v>
       </c>
       <c r="B19" t="n">
-        <v>89340</v>
+        <v>89342</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136692323</v>
       </c>
       <c r="B21" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>136692324</v>
       </c>
       <c r="B22" t="n">
-        <v>93115</v>
+        <v>93117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>136692322</v>
       </c>
       <c r="B23" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>136692305</v>
       </c>
       <c r="B54" t="n">
-        <v>87516</v>
+        <v>87518</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>136692325</v>
       </c>
       <c r="B55" t="n">
-        <v>87490</v>
+        <v>87492</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136692331</v>
       </c>
       <c r="B56" t="n">
-        <v>93440</v>
+        <v>93442</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>136692313</v>
       </c>
       <c r="B70" t="n">
-        <v>87605</v>
+        <v>87607</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136692316</v>
       </c>
       <c r="B71" t="n">
-        <v>87605</v>
+        <v>87607</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>136692333</v>
       </c>
       <c r="B72" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>136692332</v>
       </c>
       <c r="B73" t="n">
-        <v>89335</v>
+        <v>89337</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>136692328</v>
       </c>
       <c r="B74" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>136692312</v>
       </c>
       <c r="B107" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>136692311</v>
       </c>
       <c r="B5" t="n">
-        <v>93427</v>
+        <v>93440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136692320</v>
       </c>
       <c r="B6" t="n">
-        <v>93462</v>
+        <v>93475</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>136692317</v>
       </c>
       <c r="B7" t="n">
-        <v>87517</v>
+        <v>87530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136692304</v>
       </c>
       <c r="B9" t="n">
-        <v>87607</v>
+        <v>87620</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136692307</v>
       </c>
       <c r="B10" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136692334</v>
       </c>
       <c r="B11" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136692336</v>
       </c>
       <c r="B12" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136692308</v>
       </c>
       <c r="B13" t="n">
-        <v>91532</v>
+        <v>91545</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136692306</v>
       </c>
       <c r="B14" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136692329</v>
       </c>
       <c r="B15" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136692310</v>
       </c>
       <c r="B17" t="n">
-        <v>93424</v>
+        <v>93437</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>136692335</v>
       </c>
       <c r="B19" t="n">
-        <v>89342</v>
+        <v>89355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136692323</v>
       </c>
       <c r="B21" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>136692324</v>
       </c>
       <c r="B22" t="n">
-        <v>93117</v>
+        <v>93130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>136692322</v>
       </c>
       <c r="B23" t="n">
-        <v>91637</v>
+        <v>91650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>136692305</v>
       </c>
       <c r="B54" t="n">
-        <v>87518</v>
+        <v>87531</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>136692325</v>
       </c>
       <c r="B55" t="n">
-        <v>87492</v>
+        <v>87505</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136692331</v>
       </c>
       <c r="B56" t="n">
-        <v>93442</v>
+        <v>93455</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>136692313</v>
       </c>
       <c r="B70" t="n">
-        <v>87607</v>
+        <v>87620</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136692316</v>
       </c>
       <c r="B71" t="n">
-        <v>87607</v>
+        <v>87620</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>136692333</v>
       </c>
       <c r="B72" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>136692332</v>
       </c>
       <c r="B73" t="n">
-        <v>89337</v>
+        <v>89350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>136692328</v>
       </c>
       <c r="B74" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>136692312</v>
       </c>
       <c r="B107" t="n">
-        <v>93451</v>
+        <v>93464</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>136692311</v>
       </c>
       <c r="B5" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136692320</v>
       </c>
       <c r="B6" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>136692317</v>
       </c>
       <c r="B7" t="n">
-        <v>87530</v>
+        <v>87532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136692304</v>
       </c>
       <c r="B9" t="n">
-        <v>87620</v>
+        <v>87622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136692307</v>
       </c>
       <c r="B10" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136692334</v>
       </c>
       <c r="B11" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136692336</v>
       </c>
       <c r="B12" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136692308</v>
       </c>
       <c r="B13" t="n">
-        <v>91545</v>
+        <v>91547</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136692306</v>
       </c>
       <c r="B14" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136692329</v>
       </c>
       <c r="B15" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136692310</v>
       </c>
       <c r="B17" t="n">
-        <v>93437</v>
+        <v>93438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>136692335</v>
       </c>
       <c r="B19" t="n">
-        <v>89355</v>
+        <v>89357</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136692323</v>
       </c>
       <c r="B21" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>136692324</v>
       </c>
       <c r="B22" t="n">
-        <v>93130</v>
+        <v>93132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>136692322</v>
       </c>
       <c r="B23" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>136692305</v>
       </c>
       <c r="B54" t="n">
-        <v>87531</v>
+        <v>87533</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>136692325</v>
       </c>
       <c r="B55" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136692331</v>
       </c>
       <c r="B56" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>136692313</v>
       </c>
       <c r="B70" t="n">
-        <v>87620</v>
+        <v>87622</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136692316</v>
       </c>
       <c r="B71" t="n">
-        <v>87620</v>
+        <v>87622</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>136692333</v>
       </c>
       <c r="B72" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>136692332</v>
       </c>
       <c r="B73" t="n">
-        <v>89350</v>
+        <v>89352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>136692328</v>
       </c>
       <c r="B74" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>136692312</v>
       </c>
       <c r="B107" t="n">
-        <v>93464</v>
+        <v>93465</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>136692311</v>
       </c>
       <c r="B5" t="n">
-        <v>93441</v>
+        <v>93444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136692320</v>
       </c>
       <c r="B6" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>136692317</v>
       </c>
       <c r="B7" t="n">
-        <v>87532</v>
+        <v>87535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136692304</v>
       </c>
       <c r="B9" t="n">
-        <v>87622</v>
+        <v>87625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136692307</v>
       </c>
       <c r="B10" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136692334</v>
       </c>
       <c r="B11" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136692336</v>
       </c>
       <c r="B12" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136692308</v>
       </c>
       <c r="B13" t="n">
-        <v>91547</v>
+        <v>91550</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136692306</v>
       </c>
       <c r="B14" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136692329</v>
       </c>
       <c r="B15" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136692310</v>
       </c>
       <c r="B17" t="n">
-        <v>93438</v>
+        <v>93441</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>136692335</v>
       </c>
       <c r="B19" t="n">
-        <v>89357</v>
+        <v>89360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136692323</v>
       </c>
       <c r="B21" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>136692324</v>
       </c>
       <c r="B22" t="n">
-        <v>93132</v>
+        <v>93135</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>136692322</v>
       </c>
       <c r="B23" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>136692305</v>
       </c>
       <c r="B54" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>136692325</v>
       </c>
       <c r="B55" t="n">
-        <v>87507</v>
+        <v>87510</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136692331</v>
       </c>
       <c r="B56" t="n">
-        <v>93456</v>
+        <v>93459</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>136692313</v>
       </c>
       <c r="B70" t="n">
-        <v>87622</v>
+        <v>87625</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136692316</v>
       </c>
       <c r="B71" t="n">
-        <v>87622</v>
+        <v>87625</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>136692333</v>
       </c>
       <c r="B72" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>136692332</v>
       </c>
       <c r="B73" t="n">
-        <v>89352</v>
+        <v>89355</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>136692328</v>
       </c>
       <c r="B74" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>136692312</v>
       </c>
       <c r="B107" t="n">
-        <v>93465</v>
+        <v>93468</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -3214,7 +3214,7 @@
         <v>136692314</v>
       </c>
       <c r="B26" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>136692319</v>
       </c>
       <c r="B27" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
